--- a/docs/StructureDefinition-LTCCompositionBase.xlsx
+++ b/docs/StructureDefinition-LTCCompositionBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCompositionBase.xlsx
+++ b/docs/StructureDefinition-LTCCompositionBase.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="430">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -554,7 +554,7 @@
     <t>指定特定類型的composition（如病史和體檢、出院摘要、病程紀錄）。這通常等同於製作composition的目的。</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>For Composition type, LOINC is ubiquitous and strongly endorsed by HL7. Most implementation guides will require a specific LOINC code, or use LOINC as an extensible binding.</t>
   </si>
   <si>
     <t>描述composition的關鍵metadata資料項目，用於查詢/篩選。</t>
@@ -569,11 +569,19 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/loinc-type-doc-code</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.type</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Composition.category</t>
@@ -592,6 +600,15 @@
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/loinc-document-classcodes</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>DocumenttReference.category</t>
   </si>
   <si>
     <t>Composition.subject</t>
@@ -1005,7 +1022,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition)</t>
+Reference(Composition|4.0.1)</t>
   </si>
   <si>
     <t>此關係的目標文件</t>
@@ -1075,6 +1092,9 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+  </si>
+  <si>
+    <t>DocumentReference.event.code</t>
   </si>
   <si>
     <t>Composition.event.period</t>
@@ -1096,7 +1116,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1168,6 +1188,10 @@
     <t>一個用於指明小節中所含內容種類的代碼，這個代碼必須與小節的標題相一致。</t>
   </si>
   <si>
+    <t>The code identifies the section for an automated processor of the document. This is particularly relevant when using profiles to control the structure of the document.   
+If the section has content (instead of sub-sections), the section.code does not change the meaning or interpretation of the resource that is the content of the section in the comments for the section.code.</t>
+  </si>
+  <si>
     <t>提供給文件中主題的標籤是標準化的，並且可以被電腦程式識別和處理。</t>
   </si>
   <si>
@@ -1238,9 +1262,6 @@
     <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Composition.section.orderedBy</t>
   </si>
   <si>
@@ -1260,6 +1281,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/list-order</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
   </si>
   <si>
     <t>Composition.section.entry</t>
@@ -1300,6 +1324,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
   </si>
   <si>
     <t>Composition.section.section</t>
@@ -3115,7 +3142,7 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>170</v>
@@ -3188,33 +3215,33 @@
         <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>179</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3234,22 +3261,22 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3280,7 +3307,7 @@
         <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3298,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3307,33 +3334,33 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3356,19 +3383,19 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3417,7 +3444,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3435,24 +3462,24 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3475,17 +3502,17 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3534,7 +3561,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3549,27 +3576,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3592,19 +3619,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3653,7 +3680,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -3668,27 +3695,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3711,17 +3738,17 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3770,7 +3797,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3785,27 +3812,27 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3828,16 +3855,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3887,7 +3914,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -3905,13 +3932,13 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3919,10 +3946,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3948,13 +3975,13 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3983,10 +4010,10 @@
         <v>161</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4004,7 +4031,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4022,13 +4049,13 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4036,10 +4063,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4062,19 +4089,19 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4123,7 +4150,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4141,13 +4168,13 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4155,10 +4182,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4181,13 +4208,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4238,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4270,14 +4297,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4299,13 +4326,13 @@
         <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4355,7 +4382,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4387,14 +4414,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4416,16 +4443,16 @@
         <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4474,7 +4501,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4506,10 +4533,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4535,14 +4562,14 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4570,10 +4597,10 @@
         <v>161</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4591,7 +4618,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -4609,10 +4636,10 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4623,10 +4650,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4649,17 +4676,17 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4708,7 +4735,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4726,10 +4753,10 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4740,10 +4767,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4766,17 +4793,17 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4825,7 +4852,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4843,24 +4870,24 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4883,19 +4910,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4944,7 +4971,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4962,13 +4989,13 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4976,10 +5003,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5002,16 +5029,16 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5061,7 +5088,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5079,13 +5106,13 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5093,10 +5120,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5119,13 +5146,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5176,7 +5203,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5208,14 +5235,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5237,13 +5264,13 @@
         <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5293,7 +5320,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5325,14 +5352,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5354,16 +5381,16 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5412,7 +5439,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5444,10 +5471,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5473,13 +5500,13 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5508,10 +5535,10 @@
         <v>161</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5529,7 +5556,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -5547,13 +5574,13 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5561,10 +5588,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5587,13 +5614,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5644,7 +5671,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5662,13 +5689,13 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5676,10 +5703,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5702,19 +5729,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5763,7 +5790,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5781,13 +5808,13 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5795,10 +5822,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5821,13 +5848,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5878,7 +5905,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5910,14 +5937,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5939,13 +5966,13 @@
         <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5995,7 +6022,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6027,14 +6054,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6056,16 +6083,16 @@
         <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6114,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6146,10 +6173,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6169,19 +6196,19 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6207,31 +6234,31 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6240,7 +6267,7 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6249,13 +6276,13 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6263,10 +6290,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6289,13 +6316,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6346,7 +6373,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6364,13 +6391,13 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6378,10 +6405,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6404,16 +6431,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6463,7 +6490,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6481,7 +6508,7 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>166</v>
@@ -6495,10 +6522,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6521,13 +6548,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6578,7 +6605,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6590,16 +6617,16 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6610,10 +6637,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6636,13 +6663,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6693,7 +6720,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6725,14 +6752,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6754,13 +6781,13 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6810,7 +6837,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6842,14 +6869,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6871,16 +6898,16 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6929,7 +6956,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6961,14 +6988,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6987,19 +7014,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7048,7 +7075,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7066,10 +7093,10 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7080,10 +7107,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7109,16 +7136,16 @@
         <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>173</v>
+        <v>379</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7149,7 +7176,7 @@
         <v>176</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7167,7 +7194,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7176,7 +7203,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -7188,7 +7215,7 @@
         <v>179</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7199,10 +7226,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7225,17 +7252,17 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7284,7 +7311,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7302,24 +7329,24 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7342,16 +7369,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7401,7 +7428,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7422,7 +7449,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7433,10 +7460,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7462,13 +7489,13 @@
         <v>121</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7518,7 +7545,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7527,7 +7554,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -7536,10 +7563,10 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -7550,10 +7577,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7579,16 +7606,16 @@
         <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7616,10 +7643,10 @@
         <v>161</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7637,7 +7664,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7655,7 +7682,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>166</v>
@@ -7664,15 +7691,15 @@
         <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>395</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7698,16 +7725,16 @@
         <v>170</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7735,10 +7762,10 @@
         <v>115</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7756,7 +7783,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7765,7 +7792,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -7774,10 +7801,10 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>179</v>
+        <v>410</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -7788,10 +7815,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7814,16 +7841,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7873,7 +7900,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7882,7 +7909,7 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>102</v>
@@ -7891,10 +7918,10 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -7905,10 +7932,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7934,16 +7961,16 @@
         <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7971,10 +7998,10 @@
         <v>115</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7992,7 +8019,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8001,7 +8028,7 @@
         <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>178</v>
+        <v>415</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>102</v>
@@ -8010,10 +8037,10 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>179</v>
+        <v>424</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8024,10 +8051,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8053,13 +8080,13 @@
         <v>80</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8109,7 +8136,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8118,7 +8145,7 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>102</v>
@@ -8127,10 +8154,10 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTCCompositionBase.xlsx
+++ b/docs/StructureDefinition-LTCCompositionBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCompositionBase.xlsx
+++ b/docs/StructureDefinition-LTCCompositionBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
